--- a/relatorios e formularios/Visitas_Monitoramento_Sedes_Kobo.xlsx
+++ b/relatorios e formularios/Visitas_Monitoramento_Sedes_Kobo.xlsx
@@ -414,2219 +414,2761 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ORIGEM</t>
+          <t>num_sede</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>DATA_VISTORIA</t>
+          <t>nome_sede</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>HORA</t>
+          <t>fa</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>NUM_SEDE</t>
+          <t>fazenda</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>NOME_SEDE</t>
+          <t>proprietario</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>regiao</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>MATRICULA_AVALIADOR</t>
+          <t>data_vistoria</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>PRESSAO</t>
+          <t>hora_vistoria</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>NUM_BANDEIRAS</t>
+          <t>matricula</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>LARVA_PUPA</t>
+          <t>pressao</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>INSETICIDA</t>
+          <t>bandeiras</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>POSSIVEIS_CAUSADORES</t>
+          <t>larva_pupa</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>OBSERVACOES</t>
+          <t>inseticida</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>LATITUDE</t>
+          <t>possiveis_causadores</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>LONGITUDE</t>
+          <t>observacoes</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>DATA_ENVIO</t>
+          <t>lat</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>lon</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>origem</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>submetido_em</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>kobo_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>29 - Fábio Inácio</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fábio Inácio</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>09:49</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>29 - Fábio Inácio</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>65505</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>-21.57887708009862</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>-50.43273391373425</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>2026-10-28T12:50:46</t>
         </is>
+      </c>
+      <c r="T2" t="n">
+        <v>902773050</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>55 - Yueti Takata</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>308096</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>308096 - SITIO TAKATA I</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Yueti Takata</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Estrada Rural Sumidouro</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>09:50</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>55 - Yueti Takata</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>308096</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>66541</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>-21.5788762571857</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>-50.43273510961829</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-10-28T12:51:30</t>
         </is>
+      </c>
+      <c r="T3" t="n">
+        <v>902773768</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>53 - Osvaldo Cervigne</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SEM FA - FAZENDA CATARINA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Osvaldo Cervigne</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Queiroz / Vicinal Danilo Cervigne</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>09:51</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>53 - Osvaldo Cervigne</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>665504</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>-21.5788762571857</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>-50.43273510961829</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>2026-10-28T12:52:21</t>
         </is>
+      </c>
+      <c r="T4" t="n">
+        <v>902774598</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>51 - Marcos G. Laraya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>201303</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>201303 - FAZENDA SOBRADINHO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Marcos G. Laraya</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Queiroz / Vicinal Danilo Cervigne</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>09:52</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>51 - Marcos G. Laraya</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>201303</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>665509</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>-21.5788762571857</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>-50.43273510961829</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>2026-10-28T12:53:07</t>
         </is>
+      </c>
+      <c r="T5" t="n">
+        <v>902775429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>10 - Osvaldo Angelin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Osvaldo Angelin</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>09:53</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>10 - Osvaldo Angelin</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>66550</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>-21.5788762571857</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>-50.43273510961829</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>2026-10-28T12:53:53</t>
         </is>
+      </c>
+      <c r="T6" t="n">
+        <v>902776276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>16 - Rubens Fernandes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Rubens Fernandes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>09:54</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>16 - Rubens Fernandes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>68055</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Torta</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>-21.5788762571857</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>-50.43273510961829</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>2026-10-28T12:54:36</t>
         </is>
+      </c>
+      <c r="T7" t="n">
+        <v>902776991</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>5 - Edson Correia</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>308121</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>308121 - FAZENDA CONQUISTA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Edson Correia</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>09:54</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>5 - Edson Correia</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>308121</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>62055</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>-21.57887737109625</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>-50.43273332437096</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>2026-10-28T12:57:18</t>
         </is>
+      </c>
+      <c r="T8" t="n">
+        <v>902779984</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>20 - Josias Fernandes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Josias Fernandes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>09:57</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>20 - Josias Fernandes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>62079</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>2026-10-28T12:57:42</t>
         </is>
+      </c>
+      <c r="T9" t="n">
+        <v>902780339</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>75 - Eurico Bezerra</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SEM FA - SITIO NSr FATIMA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Eurico Bezerra</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vicinal Mariano Tavares do Couto</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>09:57</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>75 - Eurico Bezerra</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>62082</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>2026-10-28T12:58:16</t>
         </is>
+      </c>
+      <c r="T10" t="n">
+        <v>902780838</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>78 - Ubirajara Comino</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>307119</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>307119 - SITIO SAO MANOEL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ubirajara Comino</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vicinal Mariano Tavares do Couto</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>09:58</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>78 - Ubirajara Comino</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>307119</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>62090</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>2026-10-28T12:58:31</t>
         </is>
+      </c>
+      <c r="T11" t="n">
+        <v>902781066</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>70 - Jorge Nagib</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SEM FA - FAZENDA BOA ESPERANÇA I</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Jorge Nagib</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vicinal Mariano Tavares do Couto</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>09:58</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>70 - Jorge Nagib</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>2026-10-28T12:58:52</t>
         </is>
+      </c>
+      <c r="T12" t="n">
+        <v>902781399</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>65 - Mauro Vieira</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SEM FA - ESTANCIA ANGELICA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mauro Vieira</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vicinal Mariano Tavares do Couto</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>09:59</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>65 - Mauro Vieira</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>68090</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>2026-10-28T12:59:15</t>
         </is>
+      </c>
+      <c r="T13" t="n">
+        <v>902781785</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>63 - Claudio Grisolia</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>308007</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>308007 - FAZENDA SAO JOSE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Claudio Grisolia</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vicinal Mariano Tavares do Couto</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>09:59</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>63 - Claudio Grisolia</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>308007</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>68009</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>2026-10-28T12:59:52</t>
         </is>
+      </c>
+      <c r="T14" t="n">
+        <v>902782328</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>35 - Aldemir Fernades</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SEM FA - SITIO NSr APARECIDA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aldemir Fernades</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>35 - Aldemir Fernades</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>68000</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Torta</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>2026-10-28T13:00:10</t>
         </is>
+      </c>
+      <c r="T15" t="n">
+        <v>902782562</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>30 - Florinda Sakuno</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>308175</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>308175 - FAZENDA SAO JORGE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Florinda Sakuno</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>30 - Florinda Sakuno</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>308175</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>68005</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>2026-10-28T13:00:50</t>
         </is>
+      </c>
+      <c r="T16" t="n">
+        <v>902783133</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>42 - Osvaldo Silveira</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SEM FA - SITIO NSr APARECIDA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Osvaldo Silveira</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>42 - Osvaldo Silveira</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>68005</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>2026-10-28T13:01:09</t>
         </is>
+      </c>
+      <c r="T17" t="n">
+        <v>902783425</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>2 - João Inácio</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>João Inácio</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2 - João Inácio</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>60005</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>2026-10-28T13:01:33</t>
         </is>
+      </c>
+      <c r="T18" t="n">
+        <v>902783747</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>24 - Neide Abreu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Neide Abreu</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>24 - Neide Abreu</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Torta</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>2026-10-28T13:01:55</t>
         </is>
+      </c>
+      <c r="T19" t="n">
+        <v>902784161</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>23 - Djalma Abreu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Djalma Abreu</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>23 - Djalma Abreu</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>2026-10-28T13:02:10</t>
         </is>
+      </c>
+      <c r="T20" t="n">
+        <v>902784380</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>18 - Ademar Silva</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ademar Silva</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>10:02</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>18 - Ademar Silva</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>60001</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>2026-10-28T13:02:25</t>
         </is>
+      </c>
+      <c r="T21" t="n">
+        <v>902784579</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>22 - José Angelim</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>José Angelim</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>10:02</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>22 - José Angelim</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>60001</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>2026-10-28T13:02:55</t>
         </is>
+      </c>
+      <c r="T22" t="n">
+        <v>902784958</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>44 - Walter R. da Silva</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Walter R. da Silva</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>10:03</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>44 - Walter R. da Silva</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>60001</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>2026-10-28T13:03:58</t>
         </is>
+      </c>
+      <c r="T23" t="n">
+        <v>902786142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>3 - Adilson Colucci</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Adilson Colucci</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>10:04</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>3 - Adilson Colucci</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>60009</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>2026-10-28T13:11:31</t>
         </is>
+      </c>
+      <c r="T24" t="n">
+        <v>902793566</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>71 - Cleber Carilho</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>201431</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>201431 - FAZENDA CARRILHO IV</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cleber Carilho</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vicinal Mariano Tavares do Couto</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>10:11</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>71 - Cleber Carilho</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>201431</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>60009</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="n">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>2026-10-28T13:11:55</t>
         </is>
+      </c>
+      <c r="T25" t="n">
+        <v>902794008</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>61 - Paulo Fumia</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SEM FA - FAZENDA DONA SANTA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Paulo Fumia</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rodovia Miguel Gantus</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>10:12</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>61 - Paulo Fumia</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>60010</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>2026-10-28T13:12:20</t>
         </is>
+      </c>
+      <c r="T26" t="n">
+        <v>902794525</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>26 - João Inácio</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SEM FA - SITIO SANTO ALGOSTINHO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>João Inácio</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>10:12</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>26 - João Inácio</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>60012</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>2026-10-28T13:12:52</t>
         </is>
+      </c>
+      <c r="T27" t="n">
+        <v>902795067</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>17 - Danilo Valeriano</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Danilo Valeriano</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>10:12</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>17 - Danilo Valeriano</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>60015</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>2026-10-28T13:13:08</t>
         </is>
+      </c>
+      <c r="T28" t="n">
+        <v>902795263</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>19 - Celso Fernandes</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SEM FA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SEM FA - SEM INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Celso Fernandes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bloco FA 308121</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>10:13</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>19 - Celso Fernandes</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>SEM FA</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>60036</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>2026-10-28T13:13:29</t>
         </is>
+      </c>
+      <c r="T29" t="n">
+        <v>902795614</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KoboToolbox (Nuvem)</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>39 - Iraci Soler</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>201021</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>201021 - FAZENDA QUEIXADA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Iraci Soler</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>10:13</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>39 - Iraci Soler</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>201021</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>60035</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
         <is>
           <t>2026-10-28T13:13:45</t>
         </is>
+      </c>
+      <c r="T30" t="n">
+        <v>902795871</v>
       </c>
     </row>
   </sheetData>
@@ -2640,7 +3182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S78"/>
+  <dimension ref="A1:T78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2676,67 +3218,72 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>STATUS_VISTORIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>STATUS_TEMATICO</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DIAS_DESDE_VISTORIA</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ULTIMA_DATA</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ULTIMA_HORA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>AVALIADOR</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PRESSAO</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>BANDEIRAS</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>LARVA_PUPA</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>INSETICIDA</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>CAUSADORES</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>OBSERVACOES</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>LATITUDE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LONGITUDE</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>STATUS_MONITORAMENTO</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>STATUS_TEMATICO</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>DIAS_DESDE_ULTIMA_VISTORIA</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>TOTAL_VISTORIAS</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ULTIMA_DATA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ULTIMA_PRESSAO</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ULTIMAS_BANDEIRAS</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>ULTIMO_LARVA_PUPA</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ULTIMO_INSETICIDA</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>ULTIMOS_CAUSADORES</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ULTIMO_AVALIADOR</t>
         </is>
       </c>
     </row>
@@ -2771,33 +3318,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-21.863853</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-50.192809</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>-21.863853</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-50.192809</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2830,62 +3376,65 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>60005</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>-21.867107</v>
       </c>
-      <c r="H3" t="n">
+      <c r="T3" t="n">
         <v>-50.19613</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:01</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>60005</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -2919,62 +3468,65 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>60009</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
         <v>-21.870901</v>
       </c>
-      <c r="H4" t="n">
+      <c r="T4" t="n">
         <v>-50.200231</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:04</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>60009</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -3008,33 +3560,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-21.870586</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-50.202453</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>-21.870586</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-50.202453</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3067,62 +3618,65 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>62055</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>-21.865544</v>
       </c>
-      <c r="H6" t="n">
+      <c r="T6" t="n">
         <v>-50.203582</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:54</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>62055</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -3156,33 +3710,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-21.864625</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-50.202086</v>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>-21.864625</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-50.202086</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3215,33 +3768,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-21.862514</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-50.203886</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>-21.862514</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-50.203886</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3254,16 +3806,8 @@
           <t>8 - Paulinho Angelin</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Paulinho Angelin</t>
@@ -3274,33 +3818,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-21.864669</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-50.20815</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>-21.864669</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-50.20815</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3333,33 +3876,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-21.864767</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-50.210341</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>-21.864767</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-50.210341</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3392,58 +3934,61 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>66550</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Ausência</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Não Aplicado</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
         <v>-21.864264</v>
       </c>
-      <c r="H11" t="n">
+      <c r="T11" t="n">
         <v>-50.211731</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:53</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Baixa</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ausência</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Não Aplicado</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>66550</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -3477,33 +4022,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-21.863219</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-50.212742</v>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>-21.863219</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-50.212742</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3536,33 +4080,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-21.865718</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-50.218546</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>-21.865718</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-50.218546</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3595,33 +4138,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-21.866367</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-50.213681</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>-21.866367</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-50.213681</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3654,33 +4196,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-21.867722</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-50.212406</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>-21.867722</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-50.212406</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3713,33 +4254,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-21.868752</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-50.212166</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>-21.868752</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-50.212166</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3772,62 +4312,65 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>68055</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
         <v>-21.867479</v>
       </c>
-      <c r="H17" t="n">
+      <c r="T17" t="n">
         <v>-50.211141</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:54</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>68055</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -3861,62 +4404,65 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>60015</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
         <v>-21.866197</v>
       </c>
-      <c r="H18" t="n">
+      <c r="T18" t="n">
         <v>-50.216385</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:12</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>60015</t>
-        </is>
       </c>
     </row>
     <row r="19">
@@ -3950,62 +4496,65 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>60001</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>-21.867099</v>
       </c>
-      <c r="H19" t="n">
+      <c r="T19" t="n">
         <v>-50.224066</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:02</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>60001</t>
-        </is>
       </c>
     </row>
     <row r="20">
@@ -4039,62 +4588,65 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>60036</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
         <v>-21.860336</v>
       </c>
-      <c r="H20" t="n">
+      <c r="T20" t="n">
         <v>-50.204144</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:13</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>60036</t>
-        </is>
       </c>
     </row>
     <row r="21">
@@ -4128,62 +4680,65 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>62079</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
         <v>-21.859939</v>
       </c>
-      <c r="H21" t="n">
+      <c r="T21" t="n">
         <v>-50.208811</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:57</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>62079</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -4217,33 +4772,32 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-21.861628</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-50.214344</v>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>-21.861628</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-50.214344</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4276,58 +4830,61 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>60001</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Ausência</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Não Aplicado</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
         <v>-21.860835</v>
       </c>
-      <c r="H23" t="n">
+      <c r="T23" t="n">
         <v>-50.217003</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:02</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Baixa</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Ausência</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Não Aplicado</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>60001</t>
-        </is>
       </c>
     </row>
     <row r="24">
@@ -4361,62 +4918,65 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
         <v>-21.881297</v>
       </c>
-      <c r="H24" t="n">
+      <c r="T24" t="n">
         <v>-50.21085</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:01</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>60000</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -4450,62 +5010,65 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
         <v>-21.881803</v>
       </c>
-      <c r="H25" t="n">
+      <c r="T25" t="n">
         <v>-50.210556</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:01</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>60000</t>
-        </is>
       </c>
     </row>
     <row r="26">
@@ -4539,33 +5102,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-21.808789</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-50.233278</v>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>-21.808789</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-50.233278</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4598,62 +5160,65 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>60012</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
         <v>-21.815461</v>
       </c>
-      <c r="H27" t="n">
+      <c r="T27" t="n">
         <v>-50.228397</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:12</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>60012</t>
-        </is>
       </c>
     </row>
     <row r="28">
@@ -4687,33 +5252,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-21.819747</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-50.222492</v>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>-21.819747</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-50.222492</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4746,33 +5310,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-21.832806</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-50.228558</v>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>-21.832806</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-50.228558</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4805,62 +5368,65 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>65505</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Ausência</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Não Aplicado</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
         <v>-21.821533</v>
       </c>
-      <c r="H30" t="n">
+      <c r="T30" t="n">
         <v>-50.219483</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:49</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Ausência</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Não Aplicado</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>65505</t>
-        </is>
       </c>
     </row>
     <row r="31">
@@ -4894,62 +5460,65 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>68005</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
         <v>-21.8294</v>
       </c>
-      <c r="H31" t="n">
+      <c r="T31" t="n">
         <v>-50.210464</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:00</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>68005</t>
-        </is>
       </c>
     </row>
     <row r="32">
@@ -4983,33 +5552,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-21.835686</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-50.205978</v>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>-21.835686</v>
+      </c>
+      <c r="T32" t="n">
+        <v>-50.205978</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5042,33 +5610,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-21.836844</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-50.203842</v>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>-21.836844</v>
+      </c>
+      <c r="T33" t="n">
+        <v>-50.203842</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5081,16 +5648,8 @@
           <t>33 - Temistocles Oliveira</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Temistocles Oliveira</t>
@@ -5101,33 +5660,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-21.840983</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-50.201661</v>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>-21.840983</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-50.201661</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5160,33 +5718,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-21.841992</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-50.201869</v>
-      </c>
-      <c r="I35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>-21.841992</v>
+      </c>
+      <c r="T35" t="n">
+        <v>-50.201869</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5219,62 +5776,65 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G36" t="n">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>68000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
         <v>-21.842325</v>
       </c>
-      <c r="H36" t="n">
+      <c r="T36" t="n">
         <v>-50.201561</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:00</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>68000</t>
-        </is>
       </c>
     </row>
     <row r="37">
@@ -5308,33 +5868,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-21.842932</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-50.20068</v>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>-21.842932</v>
+      </c>
+      <c r="T37" t="n">
+        <v>-50.20068</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5367,33 +5926,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-21.844047</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-50.198905</v>
-      </c>
-      <c r="I38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>-21.844047</v>
+      </c>
+      <c r="T38" t="n">
+        <v>-50.198905</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5426,33 +5984,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-21.846069</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-50.201836</v>
-      </c>
-      <c r="I39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>-21.846069</v>
+      </c>
+      <c r="T39" t="n">
+        <v>-50.201836</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5485,62 +6042,65 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>60035</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
         <v>-21.848456</v>
       </c>
-      <c r="H40" t="n">
+      <c r="T40" t="n">
         <v>-50.199256</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:13</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>60035</t>
-        </is>
       </c>
     </row>
     <row r="41">
@@ -5574,33 +6134,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-21.856033</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-50.195106</v>
-      </c>
-      <c r="I41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>-21.856033</v>
+      </c>
+      <c r="T41" t="n">
+        <v>-50.195106</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5633,33 +6192,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-21.849086</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-50.208408</v>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>-21.849086</v>
+      </c>
+      <c r="T42" t="n">
+        <v>-50.208408</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5692,62 +6250,65 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>68005</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
         <v>-21.852667</v>
       </c>
-      <c r="H43" t="n">
+      <c r="T43" t="n">
         <v>-50.222122</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:00</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>68005</t>
-        </is>
       </c>
     </row>
     <row r="44">
@@ -5781,33 +6342,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-21.854264</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-50.214736</v>
-      </c>
-      <c r="I44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>-21.854264</v>
+      </c>
+      <c r="T44" t="n">
+        <v>-50.214736</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5840,62 +6400,65 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>60001</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
         <v>-21.854724</v>
       </c>
-      <c r="H45" t="n">
+      <c r="T45" t="n">
         <v>-50.216092</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:03</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>60001</t>
-        </is>
       </c>
     </row>
     <row r="46">
@@ -5929,33 +6492,32 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-21.853956</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-50.217186</v>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>-21.853956</v>
+      </c>
+      <c r="T46" t="n">
+        <v>-50.217186</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5988,33 +6550,32 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-21.794408</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-50.238667</v>
-      </c>
-      <c r="I47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>-21.794408</v>
+      </c>
+      <c r="T47" t="n">
+        <v>-50.238667</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6047,33 +6608,32 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-21.792047</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-50.238717</v>
-      </c>
-      <c r="I48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>-21.792047</v>
+      </c>
+      <c r="T48" t="n">
+        <v>-50.238717</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6106,33 +6666,32 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-21.790908</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-50.239428</v>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>-21.790908</v>
+      </c>
+      <c r="T49" t="n">
+        <v>-50.239428</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6165,33 +6724,32 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-21.793447</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-50.241733</v>
-      </c>
-      <c r="I50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>-21.793447</v>
+      </c>
+      <c r="T50" t="n">
+        <v>-50.241733</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6224,62 +6782,65 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>665509</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Ausência</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
         <v>-21.761336</v>
       </c>
-      <c r="H51" t="n">
+      <c r="T51" t="n">
         <v>-50.266992</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:52</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Ausência</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>665509</t>
-        </is>
       </c>
     </row>
     <row r="52">
@@ -6313,33 +6874,32 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-21.728718</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-50.283952</v>
-      </c>
-      <c r="I52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>-21.728718</v>
+      </c>
+      <c r="T52" t="n">
+        <v>-50.283952</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6372,58 +6932,61 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>665504</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Ausência</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Não Aplicado</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
         <v>-21.729621</v>
       </c>
-      <c r="H53" t="n">
+      <c r="T53" t="n">
         <v>-50.285569</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:51</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Baixa</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Ausência</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Não Aplicado</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>665504</t>
-        </is>
       </c>
     </row>
     <row r="54">
@@ -6457,33 +7020,32 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-21.727382</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-50.285691</v>
-      </c>
-      <c r="I54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>-21.727382</v>
+      </c>
+      <c r="T54" t="n">
+        <v>-50.285691</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6516,62 +7078,65 @@
           <t>Estrada Rural Sumidouro</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>66541</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
         <v>-21.794303</v>
       </c>
-      <c r="H55" t="n">
+      <c r="T55" t="n">
         <v>-50.248289</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:50</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>66541</t>
-        </is>
       </c>
     </row>
     <row r="56">
@@ -6605,33 +7170,32 @@
           <t>Estrada Rural Sumidouro</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-21.796889</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-50.255897</v>
-      </c>
-      <c r="I56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>-21.796889</v>
+      </c>
+      <c r="T56" t="n">
+        <v>-50.255897</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6664,33 +7228,32 @@
           <t>Estrada Rural Sumidouro</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-21.78029</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-50.258795</v>
-      </c>
-      <c r="I57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+      <c r="S57" t="n">
+        <v>-21.78029</v>
+      </c>
+      <c r="T57" t="n">
+        <v>-50.258795</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6723,33 +7286,32 @@
           <t>Estrada Rural Sumidouro</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-21.779272</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-50.260164</v>
-      </c>
-      <c r="I58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>-21.779272</v>
+      </c>
+      <c r="T58" t="n">
+        <v>-50.260164</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6782,33 +7344,32 @@
           <t>Rodovia Miguel Gantus</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-21.806611</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-50.247139</v>
-      </c>
-      <c r="I59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>-21.806611</v>
+      </c>
+      <c r="T59" t="n">
+        <v>-50.247139</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6841,33 +7402,32 @@
           <t>Rodovia Miguel Gantus</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-21.811872</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-50.249789</v>
-      </c>
-      <c r="I60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>-21.811872</v>
+      </c>
+      <c r="T60" t="n">
+        <v>-50.249789</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6900,58 +7460,61 @@
           <t>Rodovia Miguel Gantus</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>60010</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Ausência</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Não Aplicado</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>-21.822106</v>
       </c>
-      <c r="H61" t="n">
+      <c r="T61" t="n">
         <v>-50.268881</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:12</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Baixa</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Ausência</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Não Aplicado</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>60010</t>
-        </is>
       </c>
     </row>
     <row r="62">
@@ -6985,33 +7548,32 @@
           <t>Rodovia Miguel Gantus</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-21.852717</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-50.254881</v>
-      </c>
-      <c r="I62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>-21.852717</v>
+      </c>
+      <c r="T62" t="n">
+        <v>-50.254881</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7044,62 +7606,65 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G63" t="n">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>68009</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
         <v>-21.784725</v>
       </c>
-      <c r="H63" t="n">
+      <c r="T63" t="n">
         <v>-50.229175</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:59</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>68009</t>
-        </is>
       </c>
     </row>
     <row r="64">
@@ -7133,33 +7698,32 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-21.792339</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-50.226975</v>
-      </c>
-      <c r="I64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>-21.792339</v>
+      </c>
+      <c r="T64" t="n">
+        <v>-50.226975</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7192,62 +7756,65 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G65" t="n">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>68090</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
         <v>-21.792422</v>
       </c>
-      <c r="H65" t="n">
+      <c r="T65" t="n">
         <v>-50.226239</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:59</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>68090</t>
-        </is>
       </c>
     </row>
     <row r="66">
@@ -7281,33 +7848,32 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-21.792997</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-50.223506</v>
-      </c>
-      <c r="I66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>-21.792997</v>
+      </c>
+      <c r="T66" t="n">
+        <v>-50.223506</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7340,33 +7906,32 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-21.792928</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-50.222175</v>
-      </c>
-      <c r="I67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
+      <c r="S67" t="n">
+        <v>-21.792928</v>
+      </c>
+      <c r="T67" t="n">
+        <v>-50.222175</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7399,33 +7964,32 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-21.794419</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-50.222514</v>
-      </c>
-      <c r="I68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
+      <c r="S68" t="n">
+        <v>-21.794419</v>
+      </c>
+      <c r="T68" t="n">
+        <v>-50.222514</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7458,33 +8022,32 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-21.79352</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-50.201512</v>
-      </c>
-      <c r="I69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
+      <c r="S69" t="n">
+        <v>-21.79352</v>
+      </c>
+      <c r="T69" t="n">
+        <v>-50.201512</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7517,62 +8080,65 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G70" t="n">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>60090</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="n">
         <v>-21.795748</v>
       </c>
-      <c r="H70" t="n">
+      <c r="T70" t="n">
         <v>-50.193903</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:58</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>60090</t>
-        </is>
       </c>
     </row>
     <row r="71">
@@ -7606,62 +8172,65 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G71" t="n">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>60009</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="n">
         <v>-21.810028</v>
       </c>
-      <c r="H71" t="n">
+      <c r="T71" t="n">
         <v>-50.183781</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>1</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>28/10/2026 10:11</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>60009</t>
-        </is>
       </c>
     </row>
     <row r="72">
@@ -7695,33 +8264,32 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-21.807825</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-50.181517</v>
-      </c>
-      <c r="I72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
+      <c r="S72" t="n">
+        <v>-21.807825</v>
+      </c>
+      <c r="T72" t="n">
+        <v>-50.181517</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7754,33 +8322,32 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-21.811197</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-50.162311</v>
-      </c>
-      <c r="I73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>-21.811197</v>
+      </c>
+      <c r="T73" t="n">
+        <v>-50.162311</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7813,33 +8380,32 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-21.808835</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-50.162507</v>
-      </c>
-      <c r="I74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>-21.808835</v>
+      </c>
+      <c r="T74" t="n">
+        <v>-50.162507</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7872,62 +8438,65 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G75" t="n">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>62082</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="n">
         <v>-21.807063</v>
       </c>
-      <c r="H75" t="n">
+      <c r="T75" t="n">
         <v>-50.16158</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>1</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:57</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>62082</t>
-        </is>
       </c>
     </row>
     <row r="76">
@@ -7961,33 +8530,32 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-21.808823</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-50.159703</v>
-      </c>
-      <c r="I76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>-21.808823</v>
+      </c>
+      <c r="T76" t="n">
+        <v>-50.159703</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8020,33 +8588,32 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-21.806963</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-50.158107</v>
-      </c>
-      <c r="I77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>-21.806963</v>
+      </c>
+      <c r="T77" t="n">
+        <v>-50.158107</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8079,62 +8646,65 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G78" t="n">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Vistoriada</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Verde (&lt;= 7 dias)</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Vinhaça</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
         <v>-21.800297</v>
       </c>
-      <c r="H78" t="n">
+      <c r="T78" t="n">
         <v>-50.155733</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Visitado</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Verde (&lt;= 7 dias)</t>
-        </is>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>28/10/2026 09:58</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Presença</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>Vinhaça</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/relatorios e formularios/Visitas_Monitoramento_Sedes_Kobo.xlsx
+++ b/relatorios e formularios/Visitas_Monitoramento_Sedes_Kobo.xlsx
@@ -414,2761 +414,3245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>num_sede</t>
+          <t>ORIGEM</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>nome_sede</t>
+          <t>DATA_VISTORIA</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>fa</t>
+          <t>HORA</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>fazenda</t>
+          <t>NUM_SEDE</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>proprietario</t>
+          <t>NOME_SEDE</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>regiao</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>data_vistoria</t>
+          <t>FAZENDA</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>hora_vistoria</t>
+          <t>PROPRIETARIO</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>matricula</t>
+          <t>REGIAO</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>pressao</t>
+          <t>LATITUDE_SEDE</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>bandeiras</t>
+          <t>LONGITUDE_SEDE</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>larva_pupa</t>
+          <t>LOCALIZACAO_SEDE</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>inseticida</t>
+          <t>LINK_GOOGLE_MAPS_SEDE</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>possiveis_causadores</t>
+          <t>MATRICULA_AVALIADOR</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>observacoes</t>
+          <t>PRESSAO</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>NUM_BANDEIRAS</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>lon</t>
+          <t>LARVA_PUPA</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>origem</t>
+          <t>INSETICIDA</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>submetido_em</t>
+          <t>POSSIVEIS_CAUSADORES</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>kobo_id</t>
+          <t>OBSERVACOES</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>LATITUDE_GPS_LANCAMENTO</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>LONGITUDE_GPS_LANCAMENTO</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>DISTANCIA_SEDE_METROS</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>DATA_ENVIO</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>29 - Fábio Inácio</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Fábio Inácio</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>-21.821533</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-50.219483</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-21.821533, -50.219483</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.821533,-50.219483</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>65505</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
         <v>-21.57887708009862</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="V2" t="n">
         <v>-50.43273391373425</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="W2" t="n">
+        <v>34834.5</v>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>2026-10-28T12:50:46</t>
         </is>
-      </c>
-      <c r="T2" t="n">
-        <v>902773050</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>55 - Yueti Takata</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>308096</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>308096 - SITIO TAKATA I</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Yueti Takata</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Estrada Rural Sumidouro</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>-21.794303</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-50.248289</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-21.794303, -50.248289</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.794303,-50.248289</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>66541</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
         <v>-21.5788762571857</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="V3" t="n">
         <v>-50.43273510961829</v>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="W3" t="n">
+        <v>30610.6</v>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>2026-10-28T12:51:30</t>
         </is>
-      </c>
-      <c r="T3" t="n">
-        <v>902773768</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>53 - Osvaldo Cervigne</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>SEM FA - FAZENDA CATARINA</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Osvaldo Cervigne</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>-21.729621</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-50.285569</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-21.729621, -50.285569</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.729621,-50.285569</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>665504</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
         <v>-21.5788762571857</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="V4" t="n">
         <v>-50.43273510961829</v>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="n">
+        <v>22633.8</v>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>2026-10-28T12:52:21</t>
         </is>
-      </c>
-      <c r="T4" t="n">
-        <v>902774598</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>51 - Marcos G. Laraya</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>201303</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>201303 - FAZENDA SOBRADINHO</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Marcos G. Laraya</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>-21.761336</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-50.266992</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-21.761336, -50.266992</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.761336,-50.266992</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>665509</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
         <v>-21.5788762571857</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="V5" t="n">
         <v>-50.43273510961829</v>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="n">
+        <v>26551.3</v>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>2026-10-28T12:53:07</t>
         </is>
-      </c>
-      <c r="T5" t="n">
-        <v>902775429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>10 - Osvaldo Angelin</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Osvaldo Angelin</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>-21.864264</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-50.211731</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-21.864264, -50.211731</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.864264,-50.211731</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>66550</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
         <v>-21.5788762571857</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="V6" t="n">
         <v>-50.43273510961829</v>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="n">
+        <v>39092.4</v>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>2026-10-28T12:53:53</t>
         </is>
-      </c>
-      <c r="T6" t="n">
-        <v>902776276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>16 - Rubens Fernandes</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Rubens Fernandes</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>-21.867479</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-50.211141</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-21.867479, -50.211141</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.867479,-50.211141</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>68055</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Torta</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
         <v>-21.5788762571857</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="V7" t="n">
         <v>-50.43273510961829</v>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="W7" t="n">
+        <v>39418.3</v>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>2026-10-28T12:54:36</t>
         </is>
-      </c>
-      <c r="T7" t="n">
-        <v>902776991</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>5 - Edson Correia</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>308121</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>308121 - FAZENDA CONQUISTA</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Edson Correia</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>-21.865544</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-50.203582</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-21.865544, -50.203582</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.865544,-50.203582</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>62055</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
         <v>-21.57887737109625</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
         <v>-50.43273332437096</v>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="W8" t="n">
+        <v>39703.8</v>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>2026-10-28T12:57:18</t>
         </is>
-      </c>
-      <c r="T8" t="n">
-        <v>902779984</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>20 - Josias Fernandes</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Josias Fernandes</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>-21.859939</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-50.208811</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-21.859939, -50.208811</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.859939,-50.208811</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>62079</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="V9" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="n">
+        <v>38882.4</v>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>2026-10-28T12:57:42</t>
         </is>
-      </c>
-      <c r="T9" t="n">
-        <v>902780339</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>75 - Eurico Bezerra</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>SEM FA - SITIO NSr FATIMA</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Eurico Bezerra</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>-21.807063</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-50.16158</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-21.807063, -50.16158</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.807063,-50.16158</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>62082</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="V10" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="n">
+        <v>37798.4</v>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>2026-10-28T12:58:16</t>
         </is>
-      </c>
-      <c r="T10" t="n">
-        <v>902780838</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>78 - Ubirajara Comino</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>307119</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>307119 - SITIO SAO MANOEL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Ubirajara Comino</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>-21.800297</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-50.155733</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-21.800297, -50.155733</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.800297,-50.155733</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>62090</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="V11" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
+      <c r="W11" t="n">
+        <v>37754</v>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>2026-10-28T12:58:31</t>
         </is>
-      </c>
-      <c r="T11" t="n">
-        <v>902781066</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>70 - Jorge Nagib</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>SEM FA - FAZENDA BOA ESPERANÇA I</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Jorge Nagib</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>-21.795748</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-50.193903</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-21.795748, -50.193903</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.795748,-50.193903</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="V12" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
+      <c r="W12" t="n">
+        <v>34504.1</v>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>2026-10-28T12:58:52</t>
         </is>
-      </c>
-      <c r="T12" t="n">
-        <v>902781399</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>65 - Mauro Vieira</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>SEM FA - ESTANCIA ANGELICA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Mauro Vieira</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="n">
+        <v>-21.792422</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-50.226239</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-21.792422, -50.226239</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.792422,-50.226239</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>68090</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="V13" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
+      <c r="W13" t="n">
+        <v>31923.4</v>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>2026-10-28T12:59:15</t>
         </is>
-      </c>
-      <c r="T13" t="n">
-        <v>902781785</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>63 - Claudio Grisolia</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>308007</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>308007 - FAZENDA SAO JOSE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Claudio Grisolia</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="n">
+        <v>-21.784725</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-50.229175</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-21.784725, -50.229175</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.784725,-50.229175</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>68009</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="V14" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
+      <c r="W14" t="n">
+        <v>31086.4</v>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>2026-10-28T12:59:52</t>
         </is>
-      </c>
-      <c r="T14" t="n">
-        <v>902782328</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>35 - Aldemir Fernades</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>SEM FA - SITIO NSr APARECIDA</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Aldemir Fernades</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="n">
+        <v>-21.842325</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-50.201561</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-21.842325, -50.201561</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.842325,-50.201561</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>68000</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>Torta</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="V15" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="W15" t="n">
+        <v>37796</v>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>2026-10-28T13:00:10</t>
         </is>
-      </c>
-      <c r="T15" t="n">
-        <v>902782562</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>30 - Florinda Sakuno</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>308175</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>308175 - FAZENDA SAO JORGE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Florinda Sakuno</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="n">
+        <v>-21.8294</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-50.210464</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-21.8294, -50.210464</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.8294,-50.210464</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>68005</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="V16" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
+      <c r="W16" t="n">
+        <v>36102.1</v>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>2026-10-28T13:00:50</t>
         </is>
-      </c>
-      <c r="T16" t="n">
-        <v>902783133</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>42 - Osvaldo Silveira</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>SEM FA - SITIO NSr APARECIDA</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Osvaldo Silveira</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="n">
+        <v>-21.852667</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-50.222122</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-21.852667, -50.222122</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.852667,-50.222122</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>68005</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="V17" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
+      <c r="W17" t="n">
+        <v>37420</v>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>2026-10-28T13:01:09</t>
         </is>
-      </c>
-      <c r="T17" t="n">
-        <v>902783425</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2 - João Inácio</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>João Inácio</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>-21.867107</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-50.19613</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-21.867107, -50.19613</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.867107,-50.19613</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>60005</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="V18" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
+      <c r="W18" t="n">
+        <v>40306.2</v>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>2026-10-28T13:01:33</t>
         </is>
-      </c>
-      <c r="T18" t="n">
-        <v>902783747</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>24 - Neide Abreu</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Neide Abreu</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>-21.881803</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-50.210556</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-21.881803, -50.210556</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.881803,-50.210556</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>Torta</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="V19" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
+      <c r="W19" t="n">
+        <v>40759.4</v>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>2026-10-28T13:01:55</t>
         </is>
-      </c>
-      <c r="T19" t="n">
-        <v>902784161</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>23 - Djalma Abreu</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Djalma Abreu</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="n">
+        <v>-21.881297</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-50.21085</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-21.881297, -50.21085</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.881297,-50.21085</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="V20" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
+      <c r="W20" t="n">
+        <v>40695.8</v>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>2026-10-28T13:02:10</t>
         </is>
-      </c>
-      <c r="T20" t="n">
-        <v>902784380</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>18 - Ademar Silva</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Ademar Silva</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>-21.867099</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-50.224066</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-21.867099, -50.224066</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.867099,-50.224066</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>60001</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="V21" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
+      <c r="W21" t="n">
+        <v>38623.8</v>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>2026-10-28T13:02:25</t>
         </is>
-      </c>
-      <c r="T21" t="n">
-        <v>902784579</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>22 - José Angelim</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>José Angelim</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="n">
+        <v>-21.860835</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-50.217003</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-21.860835, -50.217003</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.860835,-50.217003</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>60001</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="V22" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
+      <c r="W22" t="n">
+        <v>38466.1</v>
+      </c>
+      <c r="X22" t="inlineStr">
         <is>
           <t>2026-10-28T13:02:55</t>
         </is>
-      </c>
-      <c r="T22" t="n">
-        <v>902784958</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>44 - Walter R. da Silva</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Walter R. da Silva</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="n">
+        <v>-21.854724</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-50.216092</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-21.854724, -50.216092</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.854724,-50.216092</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>60001</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="n">
         <v>-21.57887416487758</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="V23" t="n">
         <v>-50.43274073291771</v>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
+      <c r="W23" t="n">
+        <v>37970</v>
+      </c>
+      <c r="X23" t="inlineStr">
         <is>
           <t>2026-10-28T13:03:58</t>
         </is>
-      </c>
-      <c r="T23" t="n">
-        <v>902786142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>3 - Adilson Colucci</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Adilson Colucci</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="n">
+        <v>-21.870901</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-50.200231</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-21.870901, -50.200231</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.870901,-50.200231</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>60009</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="V24" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
+      <c r="W24" t="n">
+        <v>40388.3</v>
+      </c>
+      <c r="X24" t="inlineStr">
         <is>
           <t>2026-10-28T13:11:31</t>
         </is>
-      </c>
-      <c r="T24" t="n">
-        <v>902793566</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>71 - Cleber Carilho</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>201431</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>201431 - FAZENDA CARRILHO IV</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Cleber Carilho</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>-21.810028</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-50.183781</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-21.810028, -50.183781</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.810028,-50.183781</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>60009</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="V25" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
+      <c r="W25" t="n">
+        <v>36362.5</v>
+      </c>
+      <c r="X25" t="inlineStr">
         <is>
           <t>2026-10-28T13:11:55</t>
         </is>
-      </c>
-      <c r="T25" t="n">
-        <v>902794008</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>61 - Paulo Fumia</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>SEM FA - FAZENDA DONA SANTA</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Paulo Fumia</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Rodovia Miguel Gantus</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="n">
+        <v>-21.822106</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-50.268881</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-21.822106, -50.268881</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.822106,-50.268881</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>60010</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="V26" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
+      <c r="W26" t="n">
+        <v>31906.8</v>
+      </c>
+      <c r="X26" t="inlineStr">
         <is>
           <t>2026-10-28T13:12:20</t>
         </is>
-      </c>
-      <c r="T26" t="n">
-        <v>902794525</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>26 - João Inácio</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>SEM FA - SITIO SANTO ALGOSTINHO</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>João Inácio</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="n">
+        <v>-21.815461</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-50.228397</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-21.815461, -50.228397</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.815461,-50.228397</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>60012</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="V27" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
+      <c r="W27" t="n">
+        <v>33730.5</v>
+      </c>
+      <c r="X27" t="inlineStr">
         <is>
           <t>2026-10-28T13:12:52</t>
         </is>
-      </c>
-      <c r="T27" t="n">
-        <v>902795067</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>17 - Danilo Valeriano</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Danilo Valeriano</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="n">
+        <v>-21.866197</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-50.216385</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-21.866197, -50.216385</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.866197,-50.216385</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>60015</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="V28" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
+      <c r="W28" t="n">
+        <v>38989.3</v>
+      </c>
+      <c r="X28" t="inlineStr">
         <is>
           <t>2026-10-28T13:13:08</t>
         </is>
-      </c>
-      <c r="T28" t="n">
-        <v>902795263</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>19 - Celso Fernandes</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>SEM FA</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>SEM FA - SEM INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Celso Fernandes</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="n">
+        <v>-21.860336</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-50.204144</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-21.860336, -50.204144</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.860336,-50.204144</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>60036</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="V29" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
+      <c r="W29" t="n">
+        <v>39205.7</v>
+      </c>
+      <c r="X29" t="inlineStr">
         <is>
           <t>2026-10-28T13:13:29</t>
         </is>
-      </c>
-      <c r="T29" t="n">
-        <v>902795614</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>KoboToolbox</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>39 - Iraci Soler</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>201021</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>201021 - FAZENDA QUEIXADA</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Iraci Soler</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="n">
+        <v>-21.848456</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-50.199256</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-21.848456, -50.199256</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.848456,-50.199256</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>60035</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="n">
         <v>-21.57887702194919</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="V30" t="n">
         <v>-50.43273396180344</v>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>KoboToolbox</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
+      <c r="W30" t="n">
+        <v>38474.6</v>
+      </c>
+      <c r="X30" t="inlineStr">
         <is>
           <t>2026-10-28T13:13:45</t>
         </is>
-      </c>
-      <c r="T30" t="n">
-        <v>902795871</v>
       </c>
     </row>
   </sheetData>
@@ -3182,7 +3666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T78"/>
+  <dimension ref="A1:V78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3218,72 +3702,82 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>LATITUDE_SEDE</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LONGITUDE_SEDE</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>LOCALIZACAO_SEDE</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>LINK_GOOGLE_MAPS_SEDE</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>STATUS_VISTORIA</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>STATUS_TEMATICO</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>DIAS_DESDE_VISTORIA</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ULTIMA_DATA</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ULTIMA_HORA</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>AVALIADOR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>PRESSAO</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>BANDEIRAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>LARVA_PUPA</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>INSETICIDA</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>CAUSADORES</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>OBSERVACOES</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>LATITUDE</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>LONGITUDE</t>
         </is>
       </c>
     </row>
@@ -3318,32 +3812,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>-21.863853</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-50.192809</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-21.863853, -50.192809</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.863853,-50.192809</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>-21.863853</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-50.192809</v>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3376,66 +3880,76 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>-21.867107</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-50.19613</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-21.867107, -50.19613</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.867107,-50.19613</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>60005</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>-21.867107</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-50.19613</v>
-      </c>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3468,66 +3982,76 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>-21.870901</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-50.200231</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-21.870901, -50.200231</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.870901,-50.200231</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>10:04</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>60009</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>-21.870901</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-50.200231</v>
-      </c>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3560,32 +4084,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>-21.870586</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-50.202453</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-21.870586, -50.202453</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.870586,-50.202453</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>-21.870586</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-50.202453</v>
-      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3618,66 +4152,76 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>-21.865544</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-50.203582</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-21.865544, -50.203582</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.865544,-50.203582</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>09:54</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>62055</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>-21.865544</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-50.203582</v>
-      </c>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3710,32 +4254,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>-21.864625</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-50.202086</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-21.864625, -50.202086</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.864625,-50.202086</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>-21.864625</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-50.202086</v>
-      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3768,32 +4322,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>-21.862514</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-50.203886</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-21.862514, -50.203886</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.862514,-50.203886</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>-21.862514</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-50.203886</v>
-      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3818,32 +4382,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="n">
+        <v>-21.864669</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-50.20815</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-21.864669, -50.20815</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.864669,-50.20815</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>-21.864669</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-50.20815</v>
-      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3876,32 +4450,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="n">
+        <v>-21.864767</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-50.210341</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-21.864767, -50.210341</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.864767,-50.210341</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>-21.864767</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-50.210341</v>
-      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3934,62 +4518,72 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="n">
+        <v>-21.864264</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-50.211731</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-21.864264, -50.211731</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.864264,-50.211731</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>09:53</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>66550</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>-21.864264</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-50.211731</v>
-      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4022,32 +4616,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="n">
+        <v>-21.863219</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-50.212742</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-21.863219, -50.212742</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.863219,-50.212742</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="n">
-        <v>-21.863219</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-50.212742</v>
-      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4080,32 +4684,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="n">
+        <v>-21.865718</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-50.218546</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-21.865718, -50.218546</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.865718,-50.218546</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>-21.865718</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-50.218546</v>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4138,32 +4752,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="n">
+        <v>-21.866367</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-50.213681</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-21.866367, -50.213681</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.866367,-50.213681</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>-21.866367</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-50.213681</v>
-      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4196,32 +4820,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="n">
+        <v>-21.867722</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-50.212406</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-21.867722, -50.212406</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.867722,-50.212406</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>-21.867722</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-50.212406</v>
-      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4254,32 +4888,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="n">
+        <v>-21.868752</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-50.212166</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-21.868752, -50.212166</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.868752,-50.212166</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>-21.868752</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-50.212166</v>
-      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4312,66 +4956,76 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" t="n">
+        <v>-21.867479</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-50.211141</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-21.867479, -50.211141</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.867479,-50.211141</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>09:54</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>68055</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Torta</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>-21.867479</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-50.211141</v>
-      </c>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4404,66 +5058,76 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="n">
+        <v>-21.866197</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-50.216385</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-21.866197, -50.216385</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.866197,-50.216385</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>10:12</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>60015</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>-21.866197</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-50.216385</v>
-      </c>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4496,66 +5160,76 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="n">
+        <v>-21.867099</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-50.224066</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-21.867099, -50.224066</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.867099,-50.224066</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>10:02</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>60001</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>-21.867099</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-50.224066</v>
-      </c>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4588,66 +5262,76 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="n">
+        <v>-21.860336</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-50.204144</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-21.860336, -50.204144</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.860336,-50.204144</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>10:13</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>60036</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>-21.860336</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-50.204144</v>
-      </c>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4680,66 +5364,76 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" t="n">
+        <v>-21.859939</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-50.208811</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-21.859939, -50.208811</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.859939,-50.208811</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>09:57</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>62079</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>-21.859939</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-50.208811</v>
-      </c>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4772,32 +5466,42 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" t="n">
+        <v>-21.861628</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-50.214344</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-21.861628, -50.214344</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.861628,-50.214344</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>-21.861628</v>
-      </c>
-      <c r="T22" t="n">
-        <v>-50.214344</v>
-      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4830,62 +5534,72 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" t="n">
+        <v>-21.860835</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-50.217003</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-21.860835, -50.217003</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.860835,-50.217003</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>10:02</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>60001</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>-21.860835</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-50.217003</v>
-      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4918,66 +5632,76 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" t="n">
+        <v>-21.881297</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-50.21085</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-21.881297, -50.21085</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.881297,-50.21085</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>-21.881297</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-50.21085</v>
-      </c>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5010,66 +5734,76 @@
           <t>Bloco FA 308121</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" t="n">
+        <v>-21.881803</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-50.210556</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>-21.881803, -50.210556</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.881803,-50.210556</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Torta</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>-21.881803</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-50.210556</v>
-      </c>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5102,32 +5836,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" t="n">
+        <v>-21.808789</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-50.233278</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-21.808789, -50.233278</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.808789,-50.233278</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>-21.808789</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-50.233278</v>
-      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5160,66 +5904,76 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" t="n">
+        <v>-21.815461</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-50.228397</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-21.815461, -50.228397</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.815461,-50.228397</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>10:12</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>60012</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>-21.815461</v>
-      </c>
-      <c r="T27" t="n">
-        <v>-50.228397</v>
-      </c>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5252,32 +6006,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" t="n">
+        <v>-21.819747</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-50.222492</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-21.819747, -50.222492</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.819747,-50.222492</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>-21.819747</v>
-      </c>
-      <c r="T28" t="n">
-        <v>-50.222492</v>
-      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5310,32 +6074,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" t="n">
+        <v>-21.832806</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-50.228558</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-21.832806, -50.228558</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.832806,-50.228558</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="n">
-        <v>-21.832806</v>
-      </c>
-      <c r="T29" t="n">
-        <v>-50.228558</v>
-      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5368,66 +6142,76 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" t="n">
+        <v>-21.821533</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-50.219483</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-21.821533, -50.219483</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.821533,-50.219483</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>09:49</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>65505</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="n">
-        <v>-21.821533</v>
-      </c>
-      <c r="T30" t="n">
-        <v>-50.219483</v>
-      </c>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5460,66 +6244,76 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" t="n">
+        <v>-21.8294</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-50.210464</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-21.8294, -50.210464</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.8294,-50.210464</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>68005</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="n">
-        <v>-21.8294</v>
-      </c>
-      <c r="T31" t="n">
-        <v>-50.210464</v>
-      </c>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5552,32 +6346,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" t="n">
+        <v>-21.835686</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-50.205978</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-21.835686, -50.205978</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.835686,-50.205978</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="n">
-        <v>-21.835686</v>
-      </c>
-      <c r="T32" t="n">
-        <v>-50.205978</v>
-      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5610,32 +6414,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" t="n">
+        <v>-21.836844</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-50.203842</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-21.836844, -50.203842</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.836844,-50.203842</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
-      <c r="S33" t="n">
-        <v>-21.836844</v>
-      </c>
-      <c r="T33" t="n">
-        <v>-50.203842</v>
-      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5660,32 +6474,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" t="n">
+        <v>-21.840983</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-50.201661</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-21.840983, -50.201661</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.840983,-50.201661</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="n">
-        <v>-21.840983</v>
-      </c>
-      <c r="T34" t="n">
-        <v>-50.201661</v>
-      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5718,32 +6542,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" t="n">
+        <v>-21.841992</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-50.201869</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-21.841992, -50.201869</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.841992,-50.201869</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="n">
-        <v>-21.841992</v>
-      </c>
-      <c r="T35" t="n">
-        <v>-50.201869</v>
-      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5776,66 +6610,76 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" t="n">
+        <v>-21.842325</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-50.201561</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-21.842325, -50.201561</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.842325,-50.201561</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>68000</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Torta</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="n">
-        <v>-21.842325</v>
-      </c>
-      <c r="T36" t="n">
-        <v>-50.201561</v>
-      </c>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5868,32 +6712,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" t="n">
+        <v>-21.842932</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-50.20068</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-21.842932, -50.20068</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.842932,-50.20068</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="n">
-        <v>-21.842932</v>
-      </c>
-      <c r="T37" t="n">
-        <v>-50.20068</v>
-      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5926,32 +6780,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" t="n">
+        <v>-21.844047</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-50.198905</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-21.844047, -50.198905</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.844047,-50.198905</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="n">
-        <v>-21.844047</v>
-      </c>
-      <c r="T38" t="n">
-        <v>-50.198905</v>
-      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5984,32 +6848,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" t="n">
+        <v>-21.846069</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-50.201836</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-21.846069, -50.201836</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.846069,-50.201836</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="n">
-        <v>-21.846069</v>
-      </c>
-      <c r="T39" t="n">
-        <v>-50.201836</v>
-      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6042,66 +6916,76 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" t="n">
+        <v>-21.848456</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-50.199256</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-21.848456, -50.199256</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.848456,-50.199256</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>10:13</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>60035</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="n">
-        <v>-21.848456</v>
-      </c>
-      <c r="T40" t="n">
-        <v>-50.199256</v>
-      </c>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6134,32 +7018,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" t="n">
+        <v>-21.856033</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-50.195106</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-21.856033, -50.195106</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.856033,-50.195106</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
-      <c r="S41" t="n">
-        <v>-21.856033</v>
-      </c>
-      <c r="T41" t="n">
-        <v>-50.195106</v>
-      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6192,32 +7086,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" t="n">
+        <v>-21.849086</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-50.208408</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>-21.849086, -50.208408</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.849086,-50.208408</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="n">
-        <v>-21.849086</v>
-      </c>
-      <c r="T42" t="n">
-        <v>-50.208408</v>
-      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6250,66 +7154,76 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" t="n">
+        <v>-21.852667</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-50.222122</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-21.852667, -50.222122</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.852667,-50.222122</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>68005</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="n">
-        <v>-21.852667</v>
-      </c>
-      <c r="T43" t="n">
-        <v>-50.222122</v>
-      </c>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6342,32 +7256,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" t="n">
+        <v>-21.854264</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-50.214736</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-21.854264, -50.214736</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.854264,-50.214736</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="n">
-        <v>-21.854264</v>
-      </c>
-      <c r="T44" t="n">
-        <v>-50.214736</v>
-      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6400,66 +7324,76 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" t="n">
+        <v>-21.854724</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-50.216092</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>-21.854724, -50.216092</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.854724,-50.216092</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>10:03</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>60001</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="n">
-        <v>-21.854724</v>
-      </c>
-      <c r="T45" t="n">
-        <v>-50.216092</v>
-      </c>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6492,32 +7426,42 @@
           <t>Vicinal Francisco Curcio (QRZ / Pompeia)</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" t="n">
+        <v>-21.853956</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-50.217186</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-21.853956, -50.217186</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.853956,-50.217186</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="n">
-        <v>-21.853956</v>
-      </c>
-      <c r="T46" t="n">
-        <v>-50.217186</v>
-      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6550,32 +7494,42 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" t="n">
+        <v>-21.794408</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-50.238667</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>-21.794408, -50.238667</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.794408,-50.238667</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="n">
-        <v>-21.794408</v>
-      </c>
-      <c r="T47" t="n">
-        <v>-50.238667</v>
-      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6608,32 +7562,42 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" t="n">
+        <v>-21.792047</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-50.238717</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-21.792047, -50.238717</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.792047,-50.238717</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
-      <c r="S48" t="n">
-        <v>-21.792047</v>
-      </c>
-      <c r="T48" t="n">
-        <v>-50.238717</v>
-      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6666,32 +7630,42 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" t="n">
+        <v>-21.790908</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-50.239428</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-21.790908, -50.239428</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.790908,-50.239428</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
-      <c r="S49" t="n">
-        <v>-21.790908</v>
-      </c>
-      <c r="T49" t="n">
-        <v>-50.239428</v>
-      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6724,32 +7698,42 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" t="n">
+        <v>-21.793447</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-50.241733</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-21.793447, -50.241733</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.793447,-50.241733</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="n">
-        <v>-21.793447</v>
-      </c>
-      <c r="T50" t="n">
-        <v>-50.241733</v>
-      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6782,66 +7766,76 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" t="n">
+        <v>-21.761336</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-50.266992</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-21.761336, -50.266992</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.761336,-50.266992</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="M51" t="n">
         <v>0</v>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>09:52</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>665509</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="n">
-        <v>-21.761336</v>
-      </c>
-      <c r="T51" t="n">
-        <v>-50.266992</v>
-      </c>
+      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6874,32 +7868,42 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" t="n">
+        <v>-21.728718</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-50.283952</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-21.728718, -50.283952</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.728718,-50.283952</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
-      <c r="S52" t="n">
-        <v>-21.728718</v>
-      </c>
-      <c r="T52" t="n">
-        <v>-50.283952</v>
-      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6932,62 +7936,72 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" t="n">
+        <v>-21.729621</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-50.285569</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-21.729621, -50.285569</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.729621,-50.285569</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="M53" t="n">
         <v>0</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>09:51</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>665504</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="n">
-        <v>-21.729621</v>
-      </c>
-      <c r="T53" t="n">
-        <v>-50.285569</v>
-      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7020,32 +8034,42 @@
           <t>Queiroz / Vicinal Danilo Cervigne</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" t="n">
+        <v>-21.727382</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-50.285691</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-21.727382, -50.285691</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.727382,-50.285691</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
-      <c r="S54" t="n">
-        <v>-21.727382</v>
-      </c>
-      <c r="T54" t="n">
-        <v>-50.285691</v>
-      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7078,66 +8102,76 @@
           <t>Estrada Rural Sumidouro</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" t="n">
+        <v>-21.794303</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-50.248289</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>-21.794303, -50.248289</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.794303,-50.248289</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I55" t="n">
+      <c r="M55" t="n">
         <v>0</v>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>09:50</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>66541</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="n">
-        <v>-21.794303</v>
-      </c>
-      <c r="T55" t="n">
-        <v>-50.248289</v>
-      </c>
+      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7170,32 +8204,42 @@
           <t>Estrada Rural Sumidouro</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" t="n">
+        <v>-21.796889</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-50.255897</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-21.796889, -50.255897</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.796889,-50.255897</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
-      <c r="S56" t="n">
-        <v>-21.796889</v>
-      </c>
-      <c r="T56" t="n">
-        <v>-50.255897</v>
-      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7228,32 +8272,42 @@
           <t>Estrada Rural Sumidouro</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" t="n">
+        <v>-21.78029</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-50.258795</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-21.78029, -50.258795</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.78029,-50.258795</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
-      <c r="S57" t="n">
-        <v>-21.78029</v>
-      </c>
-      <c r="T57" t="n">
-        <v>-50.258795</v>
-      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7286,32 +8340,42 @@
           <t>Estrada Rural Sumidouro</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" t="n">
+        <v>-21.779272</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-50.260164</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-21.779272, -50.260164</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.779272,-50.260164</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
-      <c r="S58" t="n">
-        <v>-21.779272</v>
-      </c>
-      <c r="T58" t="n">
-        <v>-50.260164</v>
-      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7344,32 +8408,42 @@
           <t>Rodovia Miguel Gantus</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" t="n">
+        <v>-21.806611</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-50.247139</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-21.806611, -50.247139</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.806611,-50.247139</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
-      <c r="S59" t="n">
-        <v>-21.806611</v>
-      </c>
-      <c r="T59" t="n">
-        <v>-50.247139</v>
-      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7402,32 +8476,42 @@
           <t>Rodovia Miguel Gantus</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" t="n">
+        <v>-21.811872</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-50.249789</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-21.811872, -50.249789</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.811872,-50.249789</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
-      <c r="S60" t="n">
-        <v>-21.811872</v>
-      </c>
-      <c r="T60" t="n">
-        <v>-50.249789</v>
-      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7460,62 +8544,72 @@
           <t>Rodovia Miguel Gantus</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" t="n">
+        <v>-21.822106</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-50.268881</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-21.822106, -50.268881</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.822106,-50.268881</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="M61" t="n">
         <v>0</v>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>10:12</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>60010</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>Ausência</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>Não Aplicado</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
-        <v>-21.822106</v>
-      </c>
-      <c r="T61" t="n">
-        <v>-50.268881</v>
-      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7548,32 +8642,42 @@
           <t>Rodovia Miguel Gantus</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" t="n">
+        <v>-21.852717</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-50.254881</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-21.852717, -50.254881</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.852717,-50.254881</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
-      <c r="S62" t="n">
-        <v>-21.852717</v>
-      </c>
-      <c r="T62" t="n">
-        <v>-50.254881</v>
-      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7606,66 +8710,76 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" t="n">
+        <v>-21.784725</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-50.229175</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-21.784725, -50.229175</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.784725,-50.229175</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I63" t="n">
+      <c r="M63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>09:59</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>68009</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="n">
-        <v>-21.784725</v>
-      </c>
-      <c r="T63" t="n">
-        <v>-50.229175</v>
-      </c>
+      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7698,32 +8812,42 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" t="n">
+        <v>-21.792339</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-50.226975</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-21.792339, -50.226975</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.792339,-50.226975</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
-      <c r="S64" t="n">
-        <v>-21.792339</v>
-      </c>
-      <c r="T64" t="n">
-        <v>-50.226975</v>
-      </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7756,66 +8880,76 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" t="n">
+        <v>-21.792422</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-50.226239</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>-21.792422, -50.226239</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.792422,-50.226239</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I65" t="n">
+      <c r="M65" t="n">
         <v>0</v>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>09:59</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>68090</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="n">
-        <v>-21.792422</v>
-      </c>
-      <c r="T65" t="n">
-        <v>-50.226239</v>
-      </c>
+      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7848,32 +8982,42 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" t="n">
+        <v>-21.792997</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-50.223506</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-21.792997, -50.223506</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.792997,-50.223506</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
-      <c r="S66" t="n">
-        <v>-21.792997</v>
-      </c>
-      <c r="T66" t="n">
-        <v>-50.223506</v>
-      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7906,32 +9050,42 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" t="n">
+        <v>-21.792928</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-50.222175</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-21.792928, -50.222175</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.792928,-50.222175</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
-      <c r="S67" t="n">
-        <v>-21.792928</v>
-      </c>
-      <c r="T67" t="n">
-        <v>-50.222175</v>
-      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7964,32 +9118,42 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" t="n">
+        <v>-21.794419</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-50.222514</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>-21.794419, -50.222514</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.794419,-50.222514</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
-      <c r="S68" t="n">
-        <v>-21.794419</v>
-      </c>
-      <c r="T68" t="n">
-        <v>-50.222514</v>
-      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8022,32 +9186,42 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" t="n">
+        <v>-21.79352</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-50.201512</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-21.79352, -50.201512</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.79352,-50.201512</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
-      <c r="S69" t="n">
-        <v>-21.79352</v>
-      </c>
-      <c r="T69" t="n">
-        <v>-50.201512</v>
-      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8080,66 +9254,76 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" t="n">
+        <v>-21.795748</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-50.193903</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-21.795748, -50.193903</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.795748,-50.193903</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I70" t="n">
+      <c r="M70" t="n">
         <v>0</v>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>09:58</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="n">
-        <v>-21.795748</v>
-      </c>
-      <c r="T70" t="n">
-        <v>-50.193903</v>
-      </c>
+      <c r="V70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8172,66 +9356,76 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" t="n">
+        <v>-21.810028</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-50.183781</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-21.810028, -50.183781</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.810028,-50.183781</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I71" t="n">
+      <c r="M71" t="n">
         <v>0</v>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>10:11</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>60009</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="n">
-        <v>-21.810028</v>
-      </c>
-      <c r="T71" t="n">
-        <v>-50.183781</v>
-      </c>
+      <c r="V71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8264,32 +9458,42 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" t="n">
+        <v>-21.807825</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-50.181517</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-21.807825, -50.181517</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.807825,-50.181517</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
-      <c r="S72" t="n">
-        <v>-21.807825</v>
-      </c>
-      <c r="T72" t="n">
-        <v>-50.181517</v>
-      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8322,32 +9526,42 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" t="n">
+        <v>-21.811197</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-50.162311</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-21.811197, -50.162311</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.811197,-50.162311</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
-      <c r="S73" t="n">
-        <v>-21.811197</v>
-      </c>
-      <c r="T73" t="n">
-        <v>-50.162311</v>
-      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8380,32 +9594,42 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" t="n">
+        <v>-21.808835</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-50.162507</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-21.808835, -50.162507</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.808835,-50.162507</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
-      <c r="S74" t="n">
-        <v>-21.808835</v>
-      </c>
-      <c r="T74" t="n">
-        <v>-50.162507</v>
-      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8438,66 +9662,76 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" t="n">
+        <v>-21.807063</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-50.16158</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-21.807063, -50.16158</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.807063,-50.16158</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I75" t="n">
+      <c r="M75" t="n">
         <v>0</v>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>09:57</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>62082</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="n">
-        <v>-21.807063</v>
-      </c>
-      <c r="T75" t="n">
-        <v>-50.16158</v>
-      </c>
+      <c r="V75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8530,32 +9764,42 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" t="n">
+        <v>-21.808823</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-50.159703</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-21.808823, -50.159703</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.808823,-50.159703</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
-      <c r="S76" t="n">
-        <v>-21.808823</v>
-      </c>
-      <c r="T76" t="n">
-        <v>-50.159703</v>
-      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8588,32 +9832,42 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" t="n">
+        <v>-21.806963</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-50.158107</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-21.806963, -50.158107</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.806963,-50.158107</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>Vermelho (Sem Vistoria)</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
-      <c r="S77" t="n">
-        <v>-21.806963</v>
-      </c>
-      <c r="T77" t="n">
-        <v>-50.158107</v>
-      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8646,66 +9900,76 @@
           <t>Vicinal Mariano Tavares do Couto</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" t="n">
+        <v>-21.800297</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-50.155733</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-21.800297, -50.155733</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=-21.800297,-50.155733</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>Vistoriada</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>Verde (&lt;= 7 dias)</t>
         </is>
       </c>
-      <c r="I78" t="n">
+      <c r="M78" t="n">
         <v>0</v>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>09:58</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>62090</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>Presença</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>Vinhaça</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="n">
-        <v>-21.800297</v>
-      </c>
-      <c r="T78" t="n">
-        <v>-50.155733</v>
-      </c>
+      <c r="V78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/relatorios e formularios/Visitas_Monitoramento_Sedes_Kobo.xlsx
+++ b/relatorios e formularios/Visitas_Monitoramento_Sedes_Kobo.xlsx
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -6267,11 +6267,11 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Amarelo (8 a 15 dias)</t>
+          <t>Vermelho (&gt;= 16 dias)</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
